--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ49"/>
+  <dimension ref="A1:AZ57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1322,52 +1322,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135819199</v>
+        <v>136874545</v>
       </c>
       <c r="B8" t="n">
-        <v>96772</v>
+        <v>97590</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gökhult Hultemossen, Sm</t>
+          <t>Sjökärret, Sjökärret, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>575826</v>
+        <v>575820</v>
       </c>
       <c r="R8" t="n">
-        <v>6338771</v>
+        <v>6338835</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1391,12 +1387,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,75 +1401,75 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135819199</t>
+          <t>https://artportalen.se/Sighting/136874545</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>115173056</v>
+        <v>135819199</v>
       </c>
       <c r="B9" t="n">
-        <v>91909</v>
+        <v>96772</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>210</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Gökhult Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>575620</v>
+        <v>575826</v>
       </c>
       <c r="R9" t="n">
-        <v>6338869</v>
+        <v>6338771</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1497,22 +1493,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,27 +1514,27 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115173056</t>
+          <t>https://artportalen.se/Sighting/135819199</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134039367</v>
+        <v>115173056</v>
       </c>
       <c r="B10" t="n">
-        <v>91974</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1579,14 +1565,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575730</v>
+        <v>575620</v>
       </c>
       <c r="R10" t="n">
-        <v>6338781</v>
+        <v>6338869</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1613,12 +1599,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1634,27 +1630,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039367</t>
+          <t>https://artportalen.se/Sighting/115173056</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135819616</v>
+        <v>134039367</v>
       </c>
       <c r="B11" t="n">
-        <v>92534</v>
+        <v>91974</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1662,21 +1658,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1685,17 +1681,17 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Gökhult Hultemossen, Sm</t>
+          <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575695</v>
+        <v>575730</v>
       </c>
       <c r="R11" t="n">
-        <v>6338740</v>
+        <v>6338781</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1719,17 +1715,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Jämför bilderna med en annan helt säkert bestämd rynkskinn från en annan lokal: https://artportalen.se/Sighting/135954717</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1745,69 +1736,68 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135819616</t>
+          <t>https://artportalen.se/Sighting/134039367</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>114872798</v>
+        <v>135819616</v>
       </c>
       <c r="B12" t="n">
-        <v>96708</v>
+        <v>92534</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2180</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökhult Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575684</v>
+        <v>575695</v>
       </c>
       <c r="R12" t="n">
-        <v>6338822</v>
+        <v>6338740</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1831,12 +1821,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Jämför bilderna med en annan helt säkert bestämd rynkskinn från en annan lokal: https://artportalen.se/Sighting/135954717</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1852,27 +1847,27 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114872798</t>
+          <t>https://artportalen.se/Sighting/135819616</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134039376</v>
+        <v>114872798</v>
       </c>
       <c r="B13" t="n">
-        <v>96783</v>
+        <v>96708</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1898,16 +1893,20 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>575675</v>
+        <v>575684</v>
       </c>
       <c r="R13" t="n">
-        <v>6338821</v>
+        <v>6338822</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1934,12 +1933,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1948,6 +1947,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1965,13 +1965,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039376</t>
+          <t>https://artportalen.se/Sighting/114872798</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134039377</v>
+        <v>134039376</v>
       </c>
       <c r="B14" t="n">
         <v>96783</v>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>575819</v>
+        <v>575675</v>
       </c>
       <c r="R14" t="n">
-        <v>6338837</v>
+        <v>6338821</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2067,13 +2067,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039377</t>
+          <t>https://artportalen.se/Sighting/134039376</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134039378</v>
+        <v>134039377</v>
       </c>
       <c r="B15" t="n">
         <v>96783</v>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>575798</v>
+        <v>575819</v>
       </c>
       <c r="R15" t="n">
-        <v>6338862</v>
+        <v>6338837</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2169,13 +2169,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039378</t>
+          <t>https://artportalen.se/Sighting/134039377</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134039379</v>
+        <v>134039378</v>
       </c>
       <c r="B16" t="n">
         <v>96783</v>
@@ -2210,10 +2210,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575755</v>
+        <v>575798</v>
       </c>
       <c r="R16" t="n">
-        <v>6338857</v>
+        <v>6338862</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2271,13 +2271,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039379</t>
+          <t>https://artportalen.se/Sighting/134039378</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134039380</v>
+        <v>134039379</v>
       </c>
       <c r="B17" t="n">
         <v>96783</v>
@@ -2312,10 +2312,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>575719</v>
+        <v>575755</v>
       </c>
       <c r="R17" t="n">
-        <v>6338853</v>
+        <v>6338857</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2373,16 +2373,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039380</t>
+          <t>https://artportalen.se/Sighting/134039379</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>115434703</v>
+        <v>134039380</v>
       </c>
       <c r="B18" t="n">
-        <v>97733</v>
+        <v>96783</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2390,21 +2390,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575686</v>
+        <v>575719</v>
       </c>
       <c r="R18" t="n">
-        <v>6338891</v>
+        <v>6338853</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2444,12 +2444,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2475,16 +2475,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115434703</t>
+          <t>https://artportalen.se/Sighting/134039380</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>115474054</v>
+        <v>136874526</v>
       </c>
       <c r="B19" t="n">
-        <v>97733</v>
+        <v>96938</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2492,41 +2492,46 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2569</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Stor revmossa</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bazzania trilobata</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Gray</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Sjökärret, Sjökärret, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>575680</v>
+        <v>575841</v>
       </c>
       <c r="R19" t="n">
-        <v>6338885</v>
+        <v>6338842</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2550,22 +2555,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2574,34 +2569,33 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115474054</t>
+          <t>https://artportalen.se/Sighting/136874526</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>114872706</v>
+        <v>115434703</v>
       </c>
       <c r="B20" t="n">
-        <v>97394</v>
+        <v>97733</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2609,38 +2603,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2590</v>
+        <v>2569</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>575651</v>
+        <v>575686</v>
       </c>
       <c r="R20" t="n">
-        <v>6338972</v>
+        <v>6338891</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2667,12 +2657,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-27</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2681,7 +2671,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2699,16 +2688,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114872706</t>
+          <t>https://artportalen.se/Sighting/115434703</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>114872719</v>
+        <v>115474054</v>
       </c>
       <c r="B21" t="n">
-        <v>97394</v>
+        <v>97733</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2716,21 +2705,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2590</v>
+        <v>2569</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kornknutmossa</t>
+          <t>Stor revmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Odontoschisma denudatum</t>
+          <t>Bazzania trilobata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Mart.) Dumort</t>
+          <t>(L.) Gray</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2740,14 +2729,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>575678</v>
+        <v>575680</v>
       </c>
       <c r="R21" t="n">
-        <v>6338931</v>
+        <v>6338885</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2774,12 +2763,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2795,24 +2794,24 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114872719</t>
+          <t>https://artportalen.se/Sighting/115474054</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>114872727</v>
+        <v>114872706</v>
       </c>
       <c r="B22" t="n">
         <v>97394</v>
@@ -2851,10 +2850,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>575686</v>
+        <v>575651</v>
       </c>
       <c r="R22" t="n">
-        <v>6338891</v>
+        <v>6338972</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -2913,13 +2912,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114872727</t>
+          <t>https://artportalen.se/Sighting/114872706</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>114872769</v>
+        <v>114872719</v>
       </c>
       <c r="B23" t="n">
         <v>97394</v>
@@ -2958,10 +2957,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575684</v>
+        <v>575678</v>
       </c>
       <c r="R23" t="n">
-        <v>6338893</v>
+        <v>6338931</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3020,13 +3019,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114872769</t>
+          <t>https://artportalen.se/Sighting/114872719</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>114872789</v>
+        <v>114872727</v>
       </c>
       <c r="B24" t="n">
         <v>97394</v>
@@ -3065,10 +3064,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575667</v>
+        <v>575686</v>
       </c>
       <c r="R24" t="n">
-        <v>6338849</v>
+        <v>6338891</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3127,13 +3126,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114872789</t>
+          <t>https://artportalen.se/Sighting/114872727</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>115173183</v>
+        <v>114872769</v>
       </c>
       <c r="B25" t="n">
         <v>97394</v>
@@ -3168,14 +3167,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>575688</v>
+        <v>575684</v>
       </c>
       <c r="R25" t="n">
-        <v>6338871</v>
+        <v>6338893</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3202,22 +3201,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3233,24 +3222,24 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115173183</t>
+          <t>https://artportalen.se/Sighting/114872769</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>115173284</v>
+        <v>114872789</v>
       </c>
       <c r="B26" t="n">
         <v>97394</v>
@@ -3285,14 +3274,14 @@
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>575680</v>
+        <v>575667</v>
       </c>
       <c r="R26" t="n">
-        <v>6338897</v>
+        <v>6338849</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3319,22 +3308,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3350,24 +3329,24 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115173284</t>
+          <t>https://artportalen.se/Sighting/114872789</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>115173297</v>
+        <v>115173183</v>
       </c>
       <c r="B27" t="n">
         <v>97394</v>
@@ -3406,10 +3385,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>575651</v>
+        <v>575688</v>
       </c>
       <c r="R27" t="n">
-        <v>6338902</v>
+        <v>6338871</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3478,16 +3457,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115173297</t>
+          <t>https://artportalen.se/Sighting/115173183</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134039371</v>
+        <v>115173284</v>
       </c>
       <c r="B28" t="n">
-        <v>97471</v>
+        <v>97394</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3513,16 +3492,20 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>575685</v>
+        <v>575680</v>
       </c>
       <c r="R28" t="n">
-        <v>6338794</v>
+        <v>6338897</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3549,12 +3532,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3563,33 +3556,34 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039371</t>
+          <t>https://artportalen.se/Sighting/115173284</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134039372</v>
+        <v>115173297</v>
       </c>
       <c r="B29" t="n">
-        <v>97471</v>
+        <v>97394</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3615,16 +3609,20 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>575722</v>
+        <v>575651</v>
       </c>
       <c r="R29" t="n">
-        <v>6338748</v>
+        <v>6338902</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3651,12 +3649,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>10:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3665,33 +3673,34 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039372</t>
+          <t>https://artportalen.se/Sighting/115173297</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135819316</v>
+        <v>134039371</v>
       </c>
       <c r="B30" t="n">
-        <v>97614</v>
+        <v>97471</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3717,23 +3726,19 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Gökhult Hultemossen, Sm</t>
+          <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>575669</v>
+        <v>575685</v>
       </c>
       <c r="R30" t="n">
-        <v>6338811</v>
+        <v>6338794</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3757,12 +3762,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3771,34 +3776,33 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135819316</t>
+          <t>https://artportalen.se/Sighting/134039371</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135819339</v>
+        <v>134039372</v>
       </c>
       <c r="B31" t="n">
-        <v>97614</v>
+        <v>97471</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3824,23 +3828,19 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Gökhult Hultemossen, Sm</t>
+          <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>575669</v>
+        <v>575722</v>
       </c>
       <c r="R31" t="n">
-        <v>6338882</v>
+        <v>6338748</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3864,12 +3864,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3878,31 +3878,30 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135819339</t>
+          <t>https://artportalen.se/Sighting/134039372</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135819391</v>
+        <v>135819316</v>
       </c>
       <c r="B32" t="n">
         <v>97614</v>
@@ -3941,10 +3940,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>575690</v>
+        <v>575669</v>
       </c>
       <c r="R32" t="n">
-        <v>6338855</v>
+        <v>6338811</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4003,13 +4002,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135819391</t>
+          <t>https://artportalen.se/Sighting/135819316</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135819423</v>
+        <v>135819339</v>
       </c>
       <c r="B33" t="n">
         <v>97614</v>
@@ -4048,10 +4047,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>575647</v>
+        <v>575669</v>
       </c>
       <c r="R33" t="n">
-        <v>6338758</v>
+        <v>6338882</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4110,13 +4109,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135819423</t>
+          <t>https://artportalen.se/Sighting/135819339</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135819464</v>
+        <v>135819391</v>
       </c>
       <c r="B34" t="n">
         <v>97614</v>
@@ -4155,10 +4154,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>575644</v>
+        <v>575690</v>
       </c>
       <c r="R34" t="n">
-        <v>6338893</v>
+        <v>6338855</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4217,13 +4216,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135819464</t>
+          <t>https://artportalen.se/Sighting/135819391</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135819508</v>
+        <v>135819423</v>
       </c>
       <c r="B35" t="n">
         <v>97614</v>
@@ -4262,10 +4261,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>575666</v>
+        <v>575647</v>
       </c>
       <c r="R35" t="n">
-        <v>6338786</v>
+        <v>6338758</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4324,16 +4323,16 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135819508</t>
+          <t>https://artportalen.se/Sighting/135819423</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>114872751</v>
+        <v>135819464</v>
       </c>
       <c r="B36" t="n">
-        <v>96348</v>
+        <v>97614</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4341,21 +4340,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2810</v>
+        <v>2590</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4365,17 +4364,17 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökhult Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>575659</v>
+        <v>575644</v>
       </c>
       <c r="R36" t="n">
-        <v>6338885</v>
+        <v>6338893</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4399,12 +4398,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4420,27 +4419,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/114872751</t>
+          <t>https://artportalen.se/Sighting/135819464</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135819503</v>
+        <v>135819508</v>
       </c>
       <c r="B37" t="n">
-        <v>96676</v>
+        <v>97614</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4448,21 +4447,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2818</v>
+        <v>2590</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4538,16 +4537,16 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135819503</t>
+          <t>https://artportalen.se/Sighting/135819508</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123973813</v>
+        <v>136875093</v>
       </c>
       <c r="B38" t="n">
-        <v>92333</v>
+        <v>97626</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4555,37 +4554,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4217</v>
+        <v>2590</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Gökklint, Gökklint, Sm</t>
+          <t>Sjökärret, Sjökärret, Sm</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>575666</v>
+        <v>575687</v>
       </c>
       <c r="R38" t="n">
-        <v>6338964</v>
+        <v>6338889</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4609,12 +4608,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4629,27 +4628,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123973813</t>
+          <t>https://artportalen.se/Sighting/136875093</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134039364</v>
+        <v>136875341</v>
       </c>
       <c r="B39" t="n">
-        <v>91937</v>
+        <v>97626</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4657,37 +4656,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>2590</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Kringlemossen, Kringlemossen, Sm</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>575748</v>
+        <v>575682</v>
       </c>
       <c r="R39" t="n">
-        <v>6338783</v>
+        <v>6338936</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4711,12 +4710,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4731,68 +4730,65 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039364</t>
+          <t>https://artportalen.se/Sighting/136875341</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135819296</v>
+        <v>136876103</v>
       </c>
       <c r="B40" t="n">
-        <v>79230</v>
+        <v>97626</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>2590</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Kornknutmossa</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odontoschisma denudatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Mart.) Dumort</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Gökhult Hultemossen, Sm</t>
+          <t>Sjökärret, Sjökärret, Sm</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>575749</v>
+        <v>575704</v>
       </c>
       <c r="R40" t="n">
-        <v>6338671</v>
+        <v>6338711</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4816,12 +4812,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4830,34 +4826,33 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135819296</t>
+          <t>https://artportalen.se/Sighting/136876103</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123973504</v>
+        <v>114872751</v>
       </c>
       <c r="B41" t="n">
-        <v>57950</v>
+        <v>96348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4865,39 +4860,38 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>2810</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Hultemossen, Hultemossen, Sm</t>
+          <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575611</v>
+        <v>575659</v>
       </c>
       <c r="R41" t="n">
-        <v>6338932</v>
+        <v>6338885</v>
       </c>
       <c r="S41" t="n">
         <v>25</v>
@@ -4924,12 +4918,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4938,6 +4932,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4955,16 +4950,16 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123973504</t>
+          <t>https://artportalen.se/Sighting/114872751</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134039368</v>
+        <v>135819503</v>
       </c>
       <c r="B42" t="n">
-        <v>57972</v>
+        <v>96676</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4972,37 +4967,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>2818</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökhult Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575711</v>
+        <v>575666</v>
       </c>
       <c r="R42" t="n">
-        <v>6338746</v>
+        <v>6338786</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5026,17 +5025,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Födosöksspår</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5045,33 +5039,34 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039368</t>
+          <t>https://artportalen.se/Sighting/135819503</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134039374</v>
+        <v>123973813</v>
       </c>
       <c r="B43" t="n">
-        <v>5181</v>
+        <v>92333</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5079,37 +5074,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100526</v>
+        <v>4217</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Gökklint, Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575729</v>
+        <v>575666</v>
       </c>
       <c r="R43" t="n">
-        <v>6338794</v>
+        <v>6338964</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5133,17 +5128,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5169,16 +5159,16 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039374</t>
+          <t>https://artportalen.se/Sighting/123973813</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>115173209</v>
+        <v>136876055</v>
       </c>
       <c r="B44" t="n">
-        <v>58327</v>
+        <v>92524</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5186,49 +5176,46 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>103015</v>
+        <v>5420</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Sjökärret, Sjökärret, Sm</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>575688</v>
+        <v>575704</v>
       </c>
       <c r="R44" t="n">
-        <v>6338871</v>
+        <v>6338711</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5252,22 +5239,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5282,74 +5259,62 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115173209</t>
+          <t>https://artportalen.se/Sighting/136876055</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>115173318</v>
+        <v>134039364</v>
       </c>
       <c r="B45" t="n">
-        <v>58114</v>
+        <v>91937</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>575598</v>
+        <v>575748</v>
       </c>
       <c r="R45" t="n">
-        <v>6338927</v>
+        <v>6338783</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5376,22 +5341,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>10:30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2024-03-13</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:30</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5406,27 +5361,27 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115173318</t>
+          <t>https://artportalen.se/Sighting/134039364</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>115473966</v>
+        <v>135819296</v>
       </c>
       <c r="B46" t="n">
-        <v>58114</v>
+        <v>79230</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5434,49 +5389,40 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Gökhult Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>575648</v>
+        <v>575749</v>
       </c>
       <c r="R46" t="n">
-        <v>6338867</v>
+        <v>6338671</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5500,22 +5446,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5524,71 +5460,72 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Magnus Wadstein</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115473966</t>
+          <t>https://artportalen.se/Sighting/135819296</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134039363</v>
+        <v>136875334</v>
       </c>
       <c r="B47" t="n">
-        <v>5201</v>
+        <v>80095</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>105930</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Gökklint, Sm</t>
+          <t>Kringlemossen, Kringlemossen, Sm</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>575729</v>
+        <v>575693</v>
       </c>
       <c r="R47" t="n">
-        <v>6338794</v>
+        <v>6338934</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5612,17 +5549,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Gnaggångar och kläckhål</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5637,27 +5569,27 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134039363</t>
+          <t>https://artportalen.se/Sighting/136875334</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>115473932</v>
+        <v>123973504</v>
       </c>
       <c r="B48" t="n">
-        <v>97983</v>
+        <v>57950</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5665,38 +5597,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>221945</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+          <t>Hultemossen, Hultemossen, Sm</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>575648</v>
+        <v>575611</v>
       </c>
       <c r="R48" t="n">
-        <v>6338867</v>
+        <v>6338932</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -5723,22 +5656,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-03-27</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2025-04-11</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5747,34 +5670,33 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/115473932</t>
+          <t>https://artportalen.se/Sighting/123973504</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135819395</v>
+        <v>134039368</v>
       </c>
       <c r="B49" t="n">
-        <v>100107</v>
+        <v>57972</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5782,41 +5704,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>222364</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skärmstarr</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carex remota</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Gökhult Hultemossen, Sm</t>
+          <t>Gökklint, Sm</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>575690</v>
+        <v>575711</v>
       </c>
       <c r="R49" t="n">
-        <v>6338855</v>
+        <v>6338746</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5840,12 +5758,17 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Födosöksspår</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5854,23 +5777,943 @@
       <c r="AE49" t="b">
         <v>0</v>
       </c>
-      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Magnus Wadstein</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039368</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>134039374</v>
+      </c>
+      <c r="B50" t="n">
+        <v>5181</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>575729</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6338794</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039374</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>115173209</v>
+      </c>
+      <c r="B51" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>575688</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6338871</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115173209</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>115173318</v>
+      </c>
+      <c r="B52" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>575598</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6338927</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2024-03-13</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115173318</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>115473966</v>
+      </c>
+      <c r="B53" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>575648</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6338867</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115473966</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>136876002</v>
+      </c>
+      <c r="B54" t="n">
+        <v>58169</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Sjökärret, Sjökärret, Sm</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>575687</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6338729</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136876002</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>134039363</v>
+      </c>
+      <c r="B55" t="n">
+        <v>5201</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Gökklint, Sm</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>575729</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6338794</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Gnaggångar och kläckhål</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134039363</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>115473932</v>
+      </c>
+      <c r="B56" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Gökklint, Idhultesjön, Mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>575648</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6338867</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2024-03-27</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115473932</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>135819395</v>
+      </c>
+      <c r="B57" t="n">
+        <v>100107</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222364</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Skärmstarr</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Carex remota</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Gökhult Hultemossen, Sm</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>575690</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6338855</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF57" t="inlineStr"/>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Magnus Wadstein</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135819395</t>
         </is>
@@ -5926,6 +6769,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -1325,7 +1325,7 @@
         <v>136874545</v>
       </c>
       <c r="B8" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>136874526</v>
       </c>
       <c r="B19" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136875093</v>
       </c>
       <c r="B38" t="n">
-        <v>97626</v>
+        <v>97632</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>136875341</v>
       </c>
       <c r="B39" t="n">
-        <v>97626</v>
+        <v>97632</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>136876103</v>
       </c>
       <c r="B40" t="n">
-        <v>97626</v>
+        <v>97632</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136876055</v>
       </c>
       <c r="B44" t="n">
-        <v>92524</v>
+        <v>92526</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136875334</v>
       </c>
       <c r="B47" t="n">
-        <v>80095</v>
+        <v>80099</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -1325,7 +1325,7 @@
         <v>136874545</v>
       </c>
       <c r="B8" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>136874526</v>
       </c>
       <c r="B19" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136875093</v>
       </c>
       <c r="B38" t="n">
-        <v>97632</v>
+        <v>97634</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>136875341</v>
       </c>
       <c r="B39" t="n">
-        <v>97632</v>
+        <v>97634</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>136876103</v>
       </c>
       <c r="B40" t="n">
-        <v>97632</v>
+        <v>97634</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136876055</v>
       </c>
       <c r="B44" t="n">
-        <v>92526</v>
+        <v>92528</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136875334</v>
       </c>
       <c r="B47" t="n">
-        <v>80099</v>
+        <v>80101</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -1325,7 +1325,7 @@
         <v>136874545</v>
       </c>
       <c r="B8" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>136874526</v>
       </c>
       <c r="B19" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136875093</v>
       </c>
       <c r="B38" t="n">
-        <v>97634</v>
+        <v>97635</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>136875341</v>
       </c>
       <c r="B39" t="n">
-        <v>97634</v>
+        <v>97635</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>136876103</v>
       </c>
       <c r="B40" t="n">
-        <v>97634</v>
+        <v>97635</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136876055</v>
       </c>
       <c r="B44" t="n">
-        <v>92528</v>
+        <v>92529</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136875334</v>
       </c>
       <c r="B47" t="n">
-        <v>80101</v>
+        <v>80102</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -1325,7 +1325,7 @@
         <v>136874545</v>
       </c>
       <c r="B8" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>136874526</v>
       </c>
       <c r="B19" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136875093</v>
       </c>
       <c r="B38" t="n">
-        <v>97635</v>
+        <v>97641</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>136875341</v>
       </c>
       <c r="B39" t="n">
-        <v>97635</v>
+        <v>97641</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>136876103</v>
       </c>
       <c r="B40" t="n">
-        <v>97635</v>
+        <v>97641</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136876055</v>
       </c>
       <c r="B44" t="n">
-        <v>92529</v>
+        <v>92535</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -1325,7 +1325,7 @@
         <v>136874545</v>
       </c>
       <c r="B8" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>136874526</v>
       </c>
       <c r="B19" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136875093</v>
       </c>
       <c r="B38" t="n">
-        <v>97641</v>
+        <v>97645</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>136875341</v>
       </c>
       <c r="B39" t="n">
-        <v>97641</v>
+        <v>97645</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>136876103</v>
       </c>
       <c r="B40" t="n">
-        <v>97641</v>
+        <v>97645</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136876055</v>
       </c>
       <c r="B44" t="n">
-        <v>92535</v>
+        <v>92539</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136875334</v>
       </c>
       <c r="B47" t="n">
-        <v>80102</v>
+        <v>80104</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -1325,7 +1325,7 @@
         <v>136874545</v>
       </c>
       <c r="B8" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>136874526</v>
       </c>
       <c r="B19" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136875093</v>
       </c>
       <c r="B38" t="n">
-        <v>97645</v>
+        <v>97647</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>136875341</v>
       </c>
       <c r="B39" t="n">
-        <v>97645</v>
+        <v>97647</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>136876103</v>
       </c>
       <c r="B40" t="n">
-        <v>97645</v>
+        <v>97647</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -1325,7 +1325,7 @@
         <v>136874545</v>
       </c>
       <c r="B8" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>136874526</v>
       </c>
       <c r="B19" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136875093</v>
       </c>
       <c r="B38" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>136875341</v>
       </c>
       <c r="B39" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>136876103</v>
       </c>
       <c r="B40" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136876055</v>
       </c>
       <c r="B44" t="n">
-        <v>92539</v>
+        <v>92541</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136875334</v>
       </c>
       <c r="B47" t="n">
-        <v>80104</v>
+        <v>80107</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -1325,7 +1325,7 @@
         <v>136874545</v>
       </c>
       <c r="B8" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>136874526</v>
       </c>
       <c r="B19" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136875093</v>
       </c>
       <c r="B38" t="n">
-        <v>97649</v>
+        <v>97662</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>136875341</v>
       </c>
       <c r="B39" t="n">
-        <v>97649</v>
+        <v>97662</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>136876103</v>
       </c>
       <c r="B40" t="n">
-        <v>97649</v>
+        <v>97662</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136876055</v>
       </c>
       <c r="B44" t="n">
-        <v>92541</v>
+        <v>92554</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136875334</v>
       </c>
       <c r="B47" t="n">
-        <v>80107</v>
+        <v>80120</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>136876002</v>
       </c>
       <c r="B54" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -1325,7 +1325,7 @@
         <v>136874545</v>
       </c>
       <c r="B8" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>136874526</v>
       </c>
       <c r="B19" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136875093</v>
       </c>
       <c r="B38" t="n">
-        <v>97662</v>
+        <v>97664</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>136875341</v>
       </c>
       <c r="B39" t="n">
-        <v>97662</v>
+        <v>97664</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>136876103</v>
       </c>
       <c r="B40" t="n">
-        <v>97662</v>
+        <v>97664</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136876055</v>
       </c>
       <c r="B44" t="n">
-        <v>92554</v>
+        <v>92556</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136875334</v>
       </c>
       <c r="B47" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>136876002</v>
       </c>
       <c r="B54" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -6312,11 +6312,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Sjökärret, Sjökärret, Sm</t>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -1325,7 +1325,7 @@
         <v>136874545</v>
       </c>
       <c r="B8" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>136874526</v>
       </c>
       <c r="B19" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136875093</v>
       </c>
       <c r="B38" t="n">
-        <v>97664</v>
+        <v>97667</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>136875341</v>
       </c>
       <c r="B39" t="n">
-        <v>97664</v>
+        <v>97667</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>136876103</v>
       </c>
       <c r="B40" t="n">
-        <v>97664</v>
+        <v>97667</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136876055</v>
       </c>
       <c r="B44" t="n">
-        <v>92556</v>
+        <v>92559</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -1325,7 +1325,7 @@
         <v>136874545</v>
       </c>
       <c r="B8" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>136874526</v>
       </c>
       <c r="B19" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136875093</v>
       </c>
       <c r="B38" t="n">
-        <v>97667</v>
+        <v>97677</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>136875341</v>
       </c>
       <c r="B39" t="n">
-        <v>97667</v>
+        <v>97677</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>136876103</v>
       </c>
       <c r="B40" t="n">
-        <v>97667</v>
+        <v>97677</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136876055</v>
       </c>
       <c r="B44" t="n">
-        <v>92559</v>
+        <v>92569</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136875334</v>
       </c>
       <c r="B47" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>136876002</v>
       </c>
       <c r="B54" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -1325,7 +1325,7 @@
         <v>136874545</v>
       </c>
       <c r="B8" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>136874526</v>
       </c>
       <c r="B19" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136875093</v>
       </c>
       <c r="B38" t="n">
-        <v>97677</v>
+        <v>97678</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>136875341</v>
       </c>
       <c r="B39" t="n">
-        <v>97677</v>
+        <v>97678</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>136876103</v>
       </c>
       <c r="B40" t="n">
-        <v>97677</v>
+        <v>97678</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136876055</v>
       </c>
       <c r="B44" t="n">
-        <v>92569</v>
+        <v>92570</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -1325,7 +1325,7 @@
         <v>136874545</v>
       </c>
       <c r="B8" t="n">
-        <v>97642</v>
+        <v>97647</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>136874526</v>
       </c>
       <c r="B19" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136875093</v>
       </c>
       <c r="B38" t="n">
-        <v>97678</v>
+        <v>97683</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>136875341</v>
       </c>
       <c r="B39" t="n">
-        <v>97678</v>
+        <v>97683</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>136876103</v>
       </c>
       <c r="B40" t="n">
-        <v>97678</v>
+        <v>97683</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136876055</v>
       </c>
       <c r="B44" t="n">
-        <v>92570</v>
+        <v>92573</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136875334</v>
       </c>
       <c r="B47" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>136876002</v>
       </c>
       <c r="B54" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -1325,7 +1325,7 @@
         <v>136874545</v>
       </c>
       <c r="B8" t="n">
-        <v>97647</v>
+        <v>97649</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>136874526</v>
       </c>
       <c r="B19" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136875093</v>
       </c>
       <c r="B38" t="n">
-        <v>97683</v>
+        <v>97685</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>136875341</v>
       </c>
       <c r="B39" t="n">
-        <v>97683</v>
+        <v>97685</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>136876103</v>
       </c>
       <c r="B40" t="n">
-        <v>97683</v>
+        <v>97685</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136876055</v>
       </c>
       <c r="B44" t="n">
-        <v>92573</v>
+        <v>92575</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -1325,7 +1325,7 @@
         <v>136874545</v>
       </c>
       <c r="B8" t="n">
-        <v>97649</v>
+        <v>97655</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>136874526</v>
       </c>
       <c r="B19" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136875093</v>
       </c>
       <c r="B38" t="n">
-        <v>97685</v>
+        <v>97691</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>136875341</v>
       </c>
       <c r="B39" t="n">
-        <v>97685</v>
+        <v>97691</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>136876103</v>
       </c>
       <c r="B40" t="n">
-        <v>97685</v>
+        <v>97691</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136876055</v>
       </c>
       <c r="B44" t="n">
-        <v>92575</v>
+        <v>92580</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136875334</v>
       </c>
       <c r="B47" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>136876002</v>
       </c>
       <c r="B54" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -1325,7 +1325,7 @@
         <v>136874545</v>
       </c>
       <c r="B8" t="n">
-        <v>97655</v>
+        <v>97667</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>136874526</v>
       </c>
       <c r="B19" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136875093</v>
       </c>
       <c r="B38" t="n">
-        <v>97691</v>
+        <v>97703</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>136875341</v>
       </c>
       <c r="B39" t="n">
-        <v>97691</v>
+        <v>97703</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>136876103</v>
       </c>
       <c r="B40" t="n">
-        <v>97691</v>
+        <v>97703</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136876055</v>
       </c>
       <c r="B44" t="n">
-        <v>92580</v>
+        <v>92592</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136875334</v>
       </c>
       <c r="B47" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 21543-2026 artfynd.xlsx
+++ b/artfynd/A 21543-2026 artfynd.xlsx
@@ -1325,7 +1325,7 @@
         <v>136874545</v>
       </c>
       <c r="B8" t="n">
-        <v>97667</v>
+        <v>97668</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>136874526</v>
       </c>
       <c r="B19" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
         <v>136875093</v>
       </c>
       <c r="B38" t="n">
-        <v>97703</v>
+        <v>97704</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>136875341</v>
       </c>
       <c r="B39" t="n">
-        <v>97703</v>
+        <v>97704</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
         <v>136876103</v>
       </c>
       <c r="B40" t="n">
-        <v>97703</v>
+        <v>97704</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>136876055</v>
       </c>
       <c r="B44" t="n">
-        <v>92592</v>
+        <v>92593</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>136875334</v>
       </c>
       <c r="B47" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
